--- a/templates/template_upload_excel.xlsx
+++ b/templates/template_upload_excel.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LPiGK\Desktop\Flavia Leotta\lab_database\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LPiGK\Desktop\Flavia Leotta\lab_database\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{563BA108-10EB-4628-B0D7-EC6E9939D25B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93C49342-DB28-483A-B081-BA2FE71E8765}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{CFC8A868-97A3-4117-AEBD-5D527B3D440E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="9" xr2:uid="{CFC8A868-97A3-4117-AEBD-5D527B3D440E}"/>
   </bookViews>
   <sheets>
     <sheet name="sampling_sites" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="80">
   <si>
     <t>site_name</t>
   </si>
@@ -284,6 +284,9 @@
   </si>
   <si>
     <t>qpcr_remarks</t>
+  </si>
+  <si>
+    <t>unique_reads_map</t>
   </si>
 </sst>
 </file>
@@ -665,17 +668,17 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5454034-6535-4BFE-BCAB-60921B85BD73}">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.42578125" style="1" customWidth="1"/>
     <col min="2" max="2" width="11.140625" style="1" customWidth="1"/>
     <col min="3" max="3" width="10" customWidth="1"/>
-    <col min="4" max="4" width="16.5703125" customWidth="1"/>
-    <col min="5" max="5" width="11" customWidth="1"/>
+    <col min="4" max="5" width="16.5703125" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>48</v>
       </c>
@@ -689,6 +692,9 @@
         <v>61</v>
       </c>
       <c r="E1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F1" t="s">
         <v>62</v>
       </c>
     </row>

--- a/templates/template_upload_excel.xlsx
+++ b/templates/template_upload_excel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LPiGK\Desktop\Flavia Leotta\lab_database\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93C49342-DB28-483A-B081-BA2FE71E8765}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9B7164E-5A21-4BEA-8F59-0429655CBD37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="9" xr2:uid="{CFC8A868-97A3-4117-AEBD-5D527B3D440E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="9" xr2:uid="{CFC8A868-97A3-4117-AEBD-5D527B3D440E}"/>
   </bookViews>
   <sheets>
     <sheet name="sampling_sites" sheetId="1" r:id="rId1"/>
@@ -18,12 +18,11 @@
     <sheet name="processed_samples" sheetId="3" r:id="rId3"/>
     <sheet name="dna_extractions" sheetId="4" r:id="rId4"/>
     <sheet name="libraries" sheetId="5" r:id="rId5"/>
-    <sheet name="sequencing_run" sheetId="6" r:id="rId6"/>
-    <sheet name="sequencing_libraries" sheetId="7" r:id="rId7"/>
-    <sheet name="indexing" sheetId="8" r:id="rId8"/>
-    <sheet name="dna_sequencing" sheetId="9" r:id="rId9"/>
-    <sheet name="dna_mapping" sheetId="10" r:id="rId10"/>
-    <sheet name="sex_estimation" sheetId="11" r:id="rId11"/>
+    <sheet name="indexing" sheetId="8" r:id="rId6"/>
+    <sheet name="sequencing_run" sheetId="6" r:id="rId7"/>
+    <sheet name="dna_sequencing" sheetId="9" r:id="rId8"/>
+    <sheet name="dna_mapping" sheetId="10" r:id="rId9"/>
+    <sheet name="sex_estimation" sheetId="11" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -47,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="82">
   <si>
     <t>site_name</t>
   </si>
@@ -139,9 +138,6 @@
     <t>library_type</t>
   </si>
   <si>
-    <t>library1_date</t>
-  </si>
-  <si>
     <t>library_operator</t>
   </si>
   <si>
@@ -247,12 +243,6 @@
     <t>ci_high_95</t>
   </si>
   <si>
-    <t>assignment</t>
-  </si>
-  <si>
-    <t>assignment_min_10k_reads</t>
-  </si>
-  <si>
     <t>coord_ns</t>
   </si>
   <si>
@@ -283,18 +273,41 @@
     <t>qpcr_method</t>
   </si>
   <si>
-    <t>qpcr_remarks</t>
-  </si>
-  <si>
     <t>unique_reads_map</t>
+  </si>
+  <si>
+    <t>scraped</t>
+  </si>
+  <si>
+    <t>library_date</t>
+  </si>
+  <si>
+    <t>qpcr_remakrs</t>
+  </si>
+  <si>
+    <t>times_indexed</t>
+  </si>
+  <si>
+    <t>sex_assignment</t>
+  </si>
+  <si>
+    <t>sex_assignment_min_10k_reads</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -322,9 +335,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -648,7 +664,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -663,47 +679,11 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5454034-6535-4BFE-BCAB-60921B85BD73}">
-  <dimension ref="A1:F1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="12.42578125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="11.140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="10" customWidth="1"/>
-    <col min="4" max="5" width="16.5703125" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C1" t="s">
-        <v>60</v>
-      </c>
-      <c r="D1" t="s">
-        <v>61</v>
-      </c>
-      <c r="E1" t="s">
-        <v>79</v>
-      </c>
-      <c r="F1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB310727-56EF-48FC-8455-4EB99AE11B4F}">
   <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -717,23 +697,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>48</v>
+      <c r="A1" s="2" t="s">
+        <v>47</v>
       </c>
       <c r="B1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1" t="s">
         <v>63</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>64</v>
       </c>
-      <c r="D1" t="s">
-        <v>65</v>
-      </c>
       <c r="E1" s="1" t="s">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -743,69 +723,70 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F5A833D-76AE-4206-90D1-3D5464B047EE}">
-  <dimension ref="A1:N1"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="12.5703125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="17" style="1" customWidth="1"/>
-    <col min="4" max="4" width="18.140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="16.7109375" customWidth="1"/>
-    <col min="6" max="6" width="17.7109375" customWidth="1"/>
-    <col min="7" max="7" width="21.85546875" customWidth="1"/>
-    <col min="8" max="8" width="19.140625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="17.28515625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="19" style="1" customWidth="1"/>
-    <col min="11" max="11" width="17.140625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="19" style="1" customWidth="1"/>
-    <col min="13" max="13" width="14.140625" customWidth="1"/>
-    <col min="14" max="14" width="15.7109375" customWidth="1"/>
-    <col min="15" max="15" width="15.140625" customWidth="1"/>
+    <col min="1" max="2" width="13.140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5703125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="16.7109375" customWidth="1"/>
+    <col min="5" max="5" width="17.7109375" customWidth="1"/>
+    <col min="6" max="6" width="21.85546875" customWidth="1"/>
+    <col min="7" max="7" width="19.140625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="17.28515625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="19" style="1" customWidth="1"/>
+    <col min="10" max="10" width="17.140625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="19" style="1" customWidth="1"/>
+    <col min="12" max="12" width="14.140625" customWidth="1"/>
+    <col min="13" max="13" width="15.7109375" customWidth="1"/>
+    <col min="14" max="14" width="15.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L1" t="s">
+        <v>65</v>
+      </c>
+      <c r="M1" t="s">
+        <v>66</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="M1" t="s">
-        <v>68</v>
-      </c>
-      <c r="N1" t="s">
-        <v>69</v>
-      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B2" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -814,49 +795,52 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{837B889F-5AE7-4054-8799-0E25FB3BD485}">
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:K1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="12.85546875" style="1" customWidth="1"/>
     <col min="3" max="3" width="21.5703125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="15.42578125" customWidth="1"/>
-    <col min="5" max="5" width="12.28515625" customWidth="1"/>
-    <col min="6" max="6" width="13.28515625" style="1" customWidth="1"/>
-    <col min="7" max="8" width="17.28515625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="13" style="1" customWidth="1"/>
-    <col min="10" max="10" width="17" style="1" customWidth="1"/>
+    <col min="4" max="5" width="15.42578125" customWidth="1"/>
+    <col min="6" max="6" width="12.28515625" customWidth="1"/>
+    <col min="7" max="7" width="13.28515625" style="1" customWidth="1"/>
+    <col min="8" max="9" width="17.28515625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="13" style="1" customWidth="1"/>
+    <col min="11" max="11" width="17" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>16</v>
       </c>
       <c r="D1" t="s">
         <v>17</v>
       </c>
-      <c r="E1" t="s">
-        <v>70</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="E1" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F1" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>22</v>
       </c>
     </row>
@@ -884,13 +868,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="4" t="s">
         <v>23</v>
       </c>
       <c r="D1" s="1" t="s">
@@ -906,16 +890,16 @@
         <v>27</v>
       </c>
       <c r="H1" t="s">
+        <v>68</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>71</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -925,7 +909,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B9A4339-A066-4AB4-886E-0D9DEDC578EE}">
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:Q1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="9.140625" style="1"/>
@@ -938,41 +922,65 @@
     <col min="9" max="9" width="16.28515625" style="1" customWidth="1"/>
     <col min="10" max="10" width="19.28515625" style="1" customWidth="1"/>
     <col min="11" max="11" width="17.140625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="17.28515625" customWidth="1"/>
+    <col min="13" max="13" width="16.5703125" customWidth="1"/>
+    <col min="14" max="14" width="17.85546875" customWidth="1"/>
+    <col min="15" max="15" width="13" customWidth="1"/>
+    <col min="16" max="16" width="14.140625" customWidth="1"/>
+    <col min="17" max="17" width="20.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="4" t="s">
         <v>23</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>35</v>
+      <c r="L1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="O1" t="s">
+        <v>78</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -981,6 +989,59 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D11149A-A8E7-4FB8-8F05-ECD601AAD9C1}">
+  <dimension ref="A1:N1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11.7109375" style="1" customWidth="1"/>
+    <col min="2" max="3" width="16.5703125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="13.7109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="15" style="1" customWidth="1"/>
+    <col min="7" max="8" width="16.7109375" style="1" customWidth="1"/>
+    <col min="9" max="9" width="15.5703125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="14" style="1" customWidth="1"/>
+    <col min="11" max="11" width="16.5703125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="14.140625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="15.7109375" customWidth="1"/>
+    <col min="14" max="14" width="16.42578125" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B519C27C-3FF4-4B30-891C-2A8409079863}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -990,11 +1051,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -1002,99 +1063,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B3D47E1-6897-44D9-8CE9-E7C4C7523E73}">
-  <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="12.140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="17" style="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D11149A-A8E7-4FB8-8F05-ECD601AAD9C1}">
-  <dimension ref="A1:N1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="11.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="14.140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="13.7109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="12.7109375" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="15" style="1" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="15.5703125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="21.42578125" customWidth="1"/>
-    <col min="10" max="10" width="14" style="1" customWidth="1"/>
-    <col min="11" max="11" width="16.5703125" style="1" customWidth="1"/>
-    <col min="12" max="12" width="14.140625" style="1" customWidth="1"/>
-    <col min="13" max="13" width="15.7109375" customWidth="1"/>
-    <col min="14" max="14" width="16.42578125" style="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D1" t="s">
-        <v>39</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="I1" t="s">
-        <v>44</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="M1" t="s">
-        <v>45</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9B0CA5B-C1BF-4492-8CE6-4C7186EBB6C0}">
   <dimension ref="A1:O1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1114,50 +1083,87 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>36</v>
+      <c r="B1" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" t="s">
         <v>51</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="O1" s="1" t="s">
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5454034-6535-4BFE-BCAB-60921B85BD73}">
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.42578125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="11.140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="5" width="16.5703125" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>58</v>
+      </c>
+      <c r="C1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1" t="s">
+        <v>75</v>
+      </c>
+      <c r="F1" t="s">
+        <v>61</v>
       </c>
     </row>
   </sheetData>
